--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEW_MEXICO_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEW_MEXICO_2014.xlsx
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C110">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C156">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C224">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C230">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C468">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C728">
